--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2011/WASHINGTON_2011.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2011/WASHINGTON_2011.xlsx
@@ -2616,7 +2616,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Gral. Simon Boivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C126">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C146">
@@ -11400,7 +11400,7 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C614">
@@ -12696,7 +12696,7 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C686">
@@ -13146,7 +13146,7 @@
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C711">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C712">
@@ -17880,7 +17880,7 @@
       </c>
       <c r="B974" t="inlineStr">
         <is>
-          <t>Altzayanca</t>
+          <t>Atltzayanca</t>
         </is>
       </c>
       <c r="C974">
@@ -19860,7 +19860,7 @@
       </c>
       <c r="B1084" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C1084">
